--- a/content/costing/Not-on-price-list.xlsx
+++ b/content/costing/Not-on-price-list.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclear text (I skipped)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Not on price list'!$A$1:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Not on price list'!$A$1:$N$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -660,12 +660,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>Dry Red Chilli</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Spices &amp; Seasonings</t>
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -673,7 +673,7 @@
       <c r="E5" s="2" t="n"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -691,18 +691,18 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>the juice of one lemon</t>
+          <t>6 garlic cloves | 3 cardamom pods, green| 2 whole peppercorn | 3 cloves |6 kashmiri red chilli, dried</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dry Red Chilli</t>
+          <t>Hing (Asafoetida)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>6 garlic cloves | 3 cardamom pods, green| 2 whole peppercorn | 3 cloves |6 kashmiri red chilli, dried</t>
+          <t>pinch of hing, optional</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hing (Asafoetida)</t>
+          <t>Vegetable Stock (cube / powder)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spices &amp; Seasonings</t>
+          <t>Pantry Staples</t>
         </is>
       </c>
       <c r="C7" s="2" t="n"/>
@@ -775,23 +775,23 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>pinch of hing, optional</t>
+          <t>1/2 cup water/chicken/veg stock</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vegetable Stock (cube / powder)</t>
+          <t>Kasuri Methi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pantry Staples</t>
+          <t>Spices &amp; Seasonings</t>
         </is>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -817,23 +817,23 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1/2 cup water/chicken/veg stock</t>
+          <t>1 heaping tbsp on kasturi methi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kasuri Methi</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spices &amp; Seasonings</t>
+          <t>Vegetable</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -841,7 +841,7 @@
       <c r="E9" s="2" t="n"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -859,18 +859,18 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1 heaping tbsp on kasturi methi</t>
+          <t>1 banana</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1 banana</t>
+          <t>1 lemon</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tabasco / Hot Sauce</t>
+          <t>Chicken Sausage</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Poultry</t>
         </is>
       </c>
       <c r="C15" s="2" t="n"/>
@@ -1093,7 +1093,7 @@
       <c r="E15" s="2" t="n"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -1115,19 +1115,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1 tsp tobasco</t>
+          <t>150 grams chicken sausage</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chicken Sausage</t>
+          <t>Chilli Vinegar</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Poultry</t>
+          <t>Oils &amp; Vinegars</t>
         </is>
       </c>
       <c r="C16" s="2" t="n"/>
@@ -1135,7 +1135,7 @@
       <c r="E16" s="2" t="n"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -1153,23 +1153,23 @@
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>150 grams chicken sausage</t>
+          <t>1 tbsp chilli vinegar</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chilli Vinegar</t>
+          <t>Bird's Eye Chilli</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oils &amp; Vinegars</t>
+          <t>Vegetable</t>
         </is>
       </c>
       <c r="C17" s="2" t="n"/>
@@ -1177,7 +1177,7 @@
       <c r="E17" s="2" t="n"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -1199,19 +1199,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1 tbsp chilli vinegar</t>
+          <t>3-4 birds eye chilli, dont have then use green chillies ( adjust as per taste)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bird's Eye Chilli</t>
+          <t>Tabasco / Hot Sauce</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C18" s="2" t="n"/>
@@ -1219,7 +1219,7 @@
       <c r="E18" s="2" t="n"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -1241,19 +1241,19 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3-4 birds eye chilli, dont have then use green chillies ( adjust as per taste)</t>
+          <t>1 tsp tobasco</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lettuce (generic leaves)</t>
+          <t>Worcestershire Sauce</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C19" s="2" t="n"/>
@@ -1261,7 +1261,7 @@
       <c r="E19" s="2" t="n"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1283,19 +1283,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>lettuce leaves</t>
+          <t>1 tbsp WC sauce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Worcestershire Sauce</t>
+          <t>Kuzhambu / Rasam / Milagai Podi</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Spices &amp; Seasonings</t>
         </is>
       </c>
       <c r="C20" s="2" t="n"/>
@@ -1303,7 +1303,7 @@
       <c r="E20" s="2" t="n"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1325,19 +1325,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1 tbsp WC sauce</t>
+          <t>2 - 3 tbsp malaga podi, adjust basis how strong and flavourful your podi is</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kuzhambu / Rasam / Milagai Podi</t>
+          <t>Bok Choy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Spices &amp; Seasonings</t>
+          <t>Vegetable</t>
         </is>
       </c>
       <c r="C21" s="2" t="n"/>
@@ -1363,23 +1363,23 @@
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2 - 3 tbsp malaga podi, adjust basis how strong and flavourful your podi is</t>
+          <t>2 bunches of bok choy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bok Choy</t>
+          <t>Whole Grain / English Mustard</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C22" s="2" t="n"/>
@@ -1409,19 +1409,19 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2 bunches of bok choy</t>
+          <t>2 tsp english mustard or to your taste</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Whole Grain / English Mustard</t>
+          <t>Gouda Cheese</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Dairy &amp; Eggs</t>
         </is>
       </c>
       <c r="C23" s="2" t="n"/>
@@ -1451,19 +1451,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2 tsp english mustard or to your taste</t>
+          <t>30 grams grated gouda cheese</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gouda Cheese</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dairy &amp; Eggs</t>
+          <t>Vegetable</t>
         </is>
       </c>
       <c r="C24" s="2" t="n"/>
@@ -1471,7 +1471,7 @@
       <c r="E24" s="2" t="n"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1493,19 +1493,19 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>30 grams grated gouda cheese</t>
+          <t>1 tablespoon lime juice</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Boombayway Sauces (stir fry / sweet mustard)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>
@@ -1513,7 +1513,7 @@
       <c r="E25" s="2" t="n"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1531,23 +1531,23 @@
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1 tablespoon lime juice</t>
+          <t>2 tbsp @boombayway Lime leaf + Lemon grass Stir Fry sauce for the marinade</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Boombayway Sauces (stir fry / sweet mustard)</t>
+          <t>Roti / Tortilla Wraps (cooked)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Bread &amp; Bakery</t>
         </is>
       </c>
       <c r="C26" s="2" t="n"/>
@@ -1555,7 +1555,7 @@
       <c r="E26" s="2" t="n"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1577,19 +1577,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2 tbsp @boombayway Lime leaf + Lemon grass Stir Fry sauce for the marinade</t>
+          <t>2 tortilla wraps , use a higher protein one or whole wheat or multigrain basis your nutrition needs, even a ro</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Roti / Tortilla Wraps (cooked)</t>
+          <t>Maggi Noodles</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bread &amp; Bakery</t>
+          <t>Pantry Staples</t>
         </is>
       </c>
       <c r="C27" s="2" t="n"/>
@@ -1619,19 +1619,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2 tortilla wraps , use a higher protein one or whole wheat or multigrain basis your nutrition needs, even a ro</t>
+          <t>3 bundles of maggi noodles</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Maggi Noodles</t>
+          <t>Maggi Hot &amp; Sweet Sauce</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pantry Staples</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C28" s="2" t="n"/>
@@ -1639,7 +1639,7 @@
       <c r="E28" s="2" t="n"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1661,14 +1661,14 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3 bundles of maggi noodles</t>
+          <t>1 tbsp maggi hot and sweet sauce</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Maggi Hot &amp; Sweet Sauce</t>
+          <t>Green Chilli Paste / Red Chilli Paste</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1681,7 +1681,7 @@
       <c r="E29" s="2" t="n"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1703,19 +1703,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1 tbsp maggi hot and sweet sauce</t>
+          <t>1 tbsp red chilli paste ( use between 1 - 2 tbsp depending on how spicy you want it )</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marshmallows</t>
+          <t>Brandy / Cognac</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Flour &amp; Baking</t>
+          <t>Oils &amp; Vinegars</t>
         </is>
       </c>
       <c r="C30" s="2" t="n"/>
@@ -1723,7 +1723,7 @@
       <c r="E30" s="2" t="n"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1745,19 +1745,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1 medium mashmallow per cookie</t>
+          <t>10 ml of brandy or cognac ( reduce same Amt of cream)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Green Chilli Paste / Red Chilli Paste</t>
+          <t>Frozen Momos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Frozen Foods</t>
         </is>
       </c>
       <c r="C31" s="2" t="n"/>
@@ -1765,7 +1765,7 @@
       <c r="E31" s="2" t="n"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1787,19 +1787,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1 tbsp red chilli paste ( use between 1 - 2 tbsp depending on how spicy you want it )</t>
+          <t>16 momos, for 2 portions, either steamed or pan fried or fried</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brandy / Cognac</t>
+          <t>Coconut Yogurt</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Oils &amp; Vinegars</t>
+          <t>Dairy &amp; Eggs</t>
         </is>
       </c>
       <c r="C32" s="2" t="n"/>
@@ -1807,7 +1807,7 @@
       <c r="E32" s="2" t="n"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1825,23 +1825,23 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>10 ml of brandy or cognac ( reduce same Amt of cream)</t>
+          <t>40 grams coconut yogurt</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Strawberries</t>
+          <t>Peri Peri Masala</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Spices &amp; Seasonings</t>
         </is>
       </c>
       <c r="C33" s="2" t="n"/>
@@ -1867,23 +1867,23 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>strawberries</t>
+          <t>1 tsp peri peri masala</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Frozen Momos</t>
+          <t>Chinsu Sauce</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frozen Foods</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C34" s="2" t="n"/>
@@ -1891,7 +1891,7 @@
       <c r="E34" s="2" t="n"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1909,23 +1909,23 @@
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>16 momos, for 2 portions, either steamed or pan fried or fried</t>
+          <t>1 tsp chinsu sauce ( basically vietnamese chilli sauce) or use any you have on hand :)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cooking Spray</t>
+          <t>Black Tea</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Oils &amp; Vinegars</t>
+          <t>Pantry Staples</t>
         </is>
       </c>
       <c r="C35" s="2" t="n"/>
@@ -1933,7 +1933,7 @@
       <c r="E35" s="2" t="n"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1955,19 +1955,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Cooking spray</t>
+          <t>1 cup black tea brewed</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dulce de Leche</t>
+          <t>Marshmallows</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Flour &amp; Baking</t>
         </is>
       </c>
       <c r="C36" s="2" t="n"/>
@@ -1997,14 +1997,14 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>dulce de leche</t>
+          <t>1 medium mashmallow per cookie</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Coconut Yogurt</t>
+          <t>Gruyère</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>40 grams coconut yogurt</t>
+          <t>35 grams gruyère</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Peri Peri Masala</t>
+          <t>Tamarind (paste / ball)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Spices &amp; Seasonings</t>
+          <t>Pantry Staples</t>
         </is>
       </c>
       <c r="C38" s="2" t="n"/>
@@ -2081,19 +2081,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1 tsp peri peri masala</t>
+          <t>1 tbsp tamarind paste or small tamarind ball soaked in 2 tbsp water</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chinsu Sauce</t>
+          <t>Frozen Chicken Meatballs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Frozen Foods</t>
         </is>
       </c>
       <c r="C39" s="2" t="n"/>
@@ -2101,7 +2101,7 @@
       <c r="E39" s="2" t="n"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -2123,19 +2123,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1 tsp chinsu sauce ( basically vietnamese chilli sauce) or use any you have on hand :)</t>
+          <t>1 packet of chicken meatballs from @trystgourmet (because who has time to make them from scratch?)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Black Tea</t>
+          <t>Chilli Crisp</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pantry Staples</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C40" s="2" t="n"/>
@@ -2165,19 +2165,19 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1 cup black tea brewed</t>
+          <t>1 tsp chilli crisp</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dan Dan Sauce</t>
+          <t>Cauliflower</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Vegetable</t>
         </is>
       </c>
       <c r="C41" s="2" t="n"/>
@@ -2185,7 +2185,7 @@
       <c r="E41" s="2" t="n"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -2207,19 +2207,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Dan Dan sauce</t>
+          <t>1/2 cup cauliflower</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gruyère</t>
+          <t>French Beans</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dairy &amp; Eggs</t>
+          <t>Vegetable</t>
         </is>
       </c>
       <c r="C42" s="2" t="n"/>
@@ -2249,19 +2249,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>35 grams gruyère</t>
+          <t>1/2 cup french beans</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tamarind (paste / ball)</t>
+          <t>Oreo Biscuits</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pantry Staples</t>
+          <t>Flour &amp; Baking</t>
         </is>
       </c>
       <c r="C43" s="2" t="n"/>
@@ -2291,19 +2291,19 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1 tbsp tamarind paste or small tamarind ball soaked in 2 tbsp water</t>
+          <t>3 mini oreo packets - 46 grams each</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Frozen Chicken Meatballs</t>
+          <t>Shawarma Spice Mix</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Frozen Foods</t>
+          <t>Spices &amp; Seasonings</t>
         </is>
       </c>
       <c r="C44" s="2" t="n"/>
@@ -2333,19 +2333,19 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1 packet of chicken meatballs from @trystgourmet (because who has time to make them from scratch?)</t>
+          <t>1 tbsp shawarma spices* see notes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chilli Crisp</t>
+          <t>Lettuce (generic leaves)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sauces &amp; Condiments</t>
+          <t>Vegetable</t>
         </is>
       </c>
       <c r="C45" s="2" t="n"/>
@@ -2375,14 +2375,14 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1 tsp chilli crisp</t>
+          <t>150 grams lettuce per bowl, use iceburg, romaine or any you prefer and whats available to you</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cauliflower</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2395,7 +2395,7 @@
       <c r="E46" s="2" t="n"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -2417,19 +2417,19 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1/2 cup cauliflower</t>
+          <t>1 tsp orange zest</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>French Beans</t>
+          <t>Nutella / Chocolate Spread</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C47" s="2" t="n"/>
@@ -2459,19 +2459,19 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1/2 cup french beans</t>
+          <t>4 tbsp nutella</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Oreo Biscuits</t>
+          <t>Boondi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Flour &amp; Baking</t>
+          <t>Pantry Staples</t>
         </is>
       </c>
       <c r="C48" s="2" t="n"/>
@@ -2501,19 +2501,19 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>3 mini oreo packets - 46 grams each</t>
+          <t>1/2 cup boondi</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Shawarma Spice Mix</t>
+          <t>Strawberries</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Spices &amp; Seasonings</t>
+          <t>Vegetable</t>
         </is>
       </c>
       <c r="C49" s="2" t="n"/>
@@ -2543,19 +2543,19 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1 tbsp shawarma spices* see notes</t>
+          <t>200 grams strawberries</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Biscoff Spread</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Sauces &amp; Condiments</t>
         </is>
       </c>
       <c r="C50" s="2" t="n"/>
@@ -2563,7 +2563,7 @@
       <c r="E50" s="2" t="n"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -2585,14 +2585,14 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1 tsp orange zest</t>
+          <t>50 grams of my homemade biscoff spread (sugar free) or any topping of choice</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nutella / Chocolate Spread</t>
+          <t>Pineapple Juice</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2605,7 +2605,7 @@
       <c r="E51" s="2" t="n"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2627,14 +2627,14 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>4 tbsp nutella</t>
+          <t>200g pineapple juice</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Boondi</t>
+          <t>Atta Noodles</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2669,180 +2669,12 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1/2 cup boondi</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Cannelloni Tubes</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Pantry Staples</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="3">
-        <f>IF(AND(ISNUMBER(E53),ISNUMBER(G53)),G53/E53,"")</f>
-        <v/>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="n">
-        <v>1</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Cannelloni tubes</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Biscoff Spread</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Sauces &amp; Condiments</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="3">
-        <f>IF(AND(ISNUMBER(E54),ISNUMBER(G54)),G54/E54,"")</f>
-        <v/>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>50 grams of my homemade biscoff spread (sugar free) or any topping of choice</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Pineapple Juice</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Sauces &amp; Condiments</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="3">
-        <f>IF(AND(ISNUMBER(E55),ISNUMBER(G55)),G55/E55,"")</f>
-        <v/>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>200g pineapple juice</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Atta Noodles</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Pantry Staples</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="3">
-        <f>IF(AND(ISNUMBER(E56),ISNUMBER(G56)),G56/E56,"")</f>
-        <v/>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
           <t>50 grams atta noodles, I use @masterchow.in</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N56"/>
+  <autoFilter ref="A1:N52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2853,7 +2685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2929,7 +2761,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2955,7 +2787,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3003,25 +2835,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cheese</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cheese Block</t>
+          <t>Fresh Cream</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cheese Cubes, Cheese Slices, Cheese Spread, Cream Cheese</t>
+          <t>Coconut Cream, Cooking Cream, Cream Cheese, Cream of Tartar, Full Cream Milk, Sour Cream, Whipping Cream</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25 grams grated cheese</t>
+          <t>1/4 cup cream + 1/4 cup pasta water ( make it lighter on calories by a</t>
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
@@ -3029,25 +2861,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>cheese</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fresh Cream</t>
+          <t>Cheese Block</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Coconut Cream, Cooking Cream, Cream Cheese, Cream of Tartar, Full Cream Milk, Sour Cream, Whipping Cream</t>
+          <t>Cheese Cubes, Cheese Slices, Cheese Spread, Cream Cheese</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1/4 cup cream + 1/4 cup pasta water ( make it lighter on calories by a</t>
+          <t>25 grams grated cheese</t>
         </is>
       </c>
       <c r="F7" s="2" t="n"/>
@@ -3055,7 +2887,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sesame seeds</t>
+          <t>sugar</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3063,17 +2895,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>White Sesame Seeds</t>
+          <t>White Sugar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Black Sesame Seeds</t>
+          <t>Brown Sugar, Caster Sugar, Coconut Sugar, Demerara Sugar, Icing Sugar, Sugar Snap Peas</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sesame seeds, for ganish</t>
+          <t>1 tbsp sugar</t>
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
@@ -3081,7 +2913,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>chocolate</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3089,17 +2921,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>White Sugar</t>
+          <t>Dark Chocolate (55%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Brown Sugar, Caster Sugar, Coconut Sugar, Demerara Sugar, Icing Sugar, Sugar Snap Peas</t>
+          <t>Chocolate Chips, Dark Chocolate (70%), Milk Chocolate, White Chocolate, White Chocolate Chips</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1 tbsp sugar</t>
+          <t>220-250 g chocolate, mix of dark and milk ( choose your own blend )</t>
         </is>
       </c>
       <c r="F9" s="2" t="n"/>
@@ -3107,25 +2939,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chocolate</t>
+          <t>peanut butter</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dark Chocolate (55%)</t>
+          <t>Peanut Butter (Smooth)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Chocolate Chips, Dark Chocolate (70%), Milk Chocolate, White Chocolate, White Chocolate Chips</t>
+          <t>Peanut Butter (Crunchy)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>220-250 g chocolate, mix of dark and milk ( choose your own blend )</t>
+          <t>1 tsp peanut butter</t>
         </is>
       </c>
       <c r="F10" s="2" t="n"/>
@@ -3133,25 +2965,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>peanut butter</t>
+          <t>cinnamon</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Peanut Butter (Smooth)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Peanut Butter (Crunchy)</t>
-        </is>
-      </c>
+          <t>Cinnamon Sticks</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1 tsp peanut butter</t>
+          <t>1 tsp cinnamon, adjust as much or as little as you like</t>
         </is>
       </c>
       <c r="F11" s="2" t="n"/>
@@ -3159,7 +2987,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cinnamon</t>
+          <t>oats</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3167,13 +2995,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cinnamon Sticks</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Rolled Oats</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Instant Oats, Oat Flour, Steel Cut Oats</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1 tsp cinnamon, adjust as much or as little as you like</t>
+          <t>1/2 cup oats</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
@@ -3181,25 +3013,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>oats</t>
+          <t>pasta</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rolled Oats</t>
+          <t>Penne</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Instant Oats, Oat Flour, Steel Cut Oats</t>
+          <t>Pizza &amp; Pasta Sauce</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1/2 cup oats</t>
+          <t>80 grams pasta, uncooked</t>
         </is>
       </c>
       <c r="F13" s="2" t="n"/>
@@ -3207,25 +3039,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>dark chocolate</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Penne</t>
+          <t>Dark Chocolate (55%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pizza &amp; Pasta Sauce</t>
+          <t>Dark Chocolate (70%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80 grams pasta, uncooked</t>
+          <t xml:space="preserve">2-3 pieces ( 15 grams ) of dark chocolate, melted ( i used bournville </t>
         </is>
       </c>
       <c r="F14" s="2" t="n"/>
@@ -3233,7 +3065,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dark chocolate</t>
+          <t>rice</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3241,17 +3073,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dark Chocolate (55%)</t>
+          <t>Basmati Rice</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dark Chocolate (70%)</t>
+          <t>Arborio Rice, Brown Rice, Jasmine Rice, Rice Bran Oil, Rice Flour, Rice Noodles, Rice Paper Sheets, Rice Vermicelli</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-3 pieces ( 15 grams ) of dark chocolate, melted ( i used bournville </t>
+          <t>2 cups cooked rice</t>
         </is>
       </c>
       <c r="F15" s="2" t="n"/>
@@ -3259,25 +3091,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mustard</t>
+          <t>chilli</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dijon Mustard</t>
+          <t>Green Chilli</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Honey Mustard, Mustard Oil, Mustard Seeds, Wholegrain Mustard, Yellow Mustard</t>
+          <t>Chili Oil, Chilli Garlic Sauce, Green Chilli Sauce, Kashmiri Chilli Powder, Red Chilli Powder, Red Chilli Sauce, Sweet Chilli Sauce</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1 tbsp mustard</t>
+          <t>1 chilli, thinly sliced</t>
         </is>
       </c>
       <c r="F16" s="2" t="n"/>
@@ -3285,25 +3117,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rice</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Basmati Rice</t>
+          <t>White Bread</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Arborio Rice, Brown Rice, Jasmine Rice, Rice Bran Oil, Rice Flour, Rice Noodles, Rice Paper Sheets, Rice Vermicelli</t>
+          <t>Bread Crumbs, Bread Flour, Garlic Bread, Lebanese Bread, Multigrain Bread, Pita Bread, Whole Wheat Bread</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2 cups cooked rice</t>
+          <t>2 slices of bread, i use theobroma sourdough and add macros accordingl</t>
         </is>
       </c>
       <c r="F17" s="2" t="n"/>
@@ -3311,7 +3143,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>chilli</t>
+          <t>cheddar cheese</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3319,17 +3151,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Green Chilli</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Chili Oil, Chilli Garlic Sauce, Green Chilli Sauce, Kashmiri Chilli Powder, Red Chilli Powder, Red Chilli Sauce, Sweet Chilli Sauce</t>
-        </is>
-      </c>
+          <t>Cheddar</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1 chilli, thinly sliced</t>
+          <t>30 grams cheddar cheese, grated</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
@@ -3337,7 +3165,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>mustard</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3345,17 +3173,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>White Bread</t>
+          <t>Dijon Mustard</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bread Crumbs, Bread Flour, Garlic Bread, Lebanese Bread, Multigrain Bread, Pita Bread, Whole Wheat Bread</t>
+          <t>Honey Mustard, Mustard Oil, Mustard Seeds, Wholegrain Mustard, Yellow Mustard</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2 slices of bread, i use theobroma sourdough and add macros accordingl</t>
+          <t>1 tbsp mustard</t>
         </is>
       </c>
       <c r="F19" s="2" t="n"/>
@@ -3363,7 +3191,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cheddar cheese</t>
+          <t>sesame seeds</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3371,13 +3199,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cheddar</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>White Sesame Seeds</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Black Sesame Seeds</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>30 grams cheddar cheese, grated</t>
+          <t>1 tbsp sesame seeds</t>
         </is>
       </c>
       <c r="F20" s="2" t="n"/>
@@ -3385,7 +3217,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noodles</t>
+          <t>vanilla</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3393,17 +3225,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hakka Noodles</t>
+          <t>Vanilla Extract</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Egg Noodles, Ramen Noodles, Rice Noodles, Soba Noodles, Udon Noodles</t>
+          <t>Vanilla Bean Paste</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>180 grams noodles, uncooked ( serving would be 60 grams per serving- t</t>
+          <t>1 tsp vanilla</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
@@ -3411,7 +3243,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>dal</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -3419,17 +3251,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vanilla Extract</t>
+          <t>(none yet)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Vanilla Bean Paste</t>
+          <t>chana dal, masoor dal, moong dal, toor dal, urad dal</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1 tsp vanilla</t>
+          <t>1/2 cup dal (toor or moong), rinsed till water runs clear and soak for</t>
         </is>
       </c>
       <c r="F22" s="2" t="n"/>
@@ -3437,25 +3269,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sourdough</t>
+          <t>bell pepper</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sourdough Slices</t>
+          <t>Bell Pepper Red</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sourdough Loaf</t>
+          <t>Bell Pepper Orange, Bell Pepper Yellow</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2 slices sourdough, toasted</t>
+          <t>1 bell pepper, cubed ( i used a mix of green, yellow and red )</t>
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
@@ -3463,25 +3295,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dry</t>
+          <t>noodles</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(none yet)</t>
+          <t>Hakka Noodles</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>active dry yeast, instant dry yeast, dry coconut (copra), dry ginger powder</t>
+          <t>Egg Noodles, Ramen Noodles, Rice Noodles, Soba Noodles, Udon Noodles</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dry</t>
+          <t>180 grams noodles, uncooked ( serving would be 60 grams per serving- t</t>
         </is>
       </c>
       <c r="F24" s="2" t="n"/>
@@ -3489,25 +3321,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dal</t>
+          <t>paprika</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(none yet)</t>
+          <t>Smoked Paprika</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>chana dal, masoor dal, moong dal, toor dal, urad dal</t>
+          <t>Sweet Paprika</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1/2 cup dal (toor or moong), rinsed till water runs clear and soak for</t>
+          <t>1 tsp paprika</t>
         </is>
       </c>
       <c r="F25" s="2" t="n"/>
@@ -3515,7 +3347,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mango</t>
+          <t>chilli powder</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -3523,17 +3355,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frozen Mango Chunks</t>
+          <t>Red Chilli Powder</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Raw Mango</t>
+          <t>Kashmiri Chilli Powder</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mango, i use frozen mangoes that i keep in the freezer, allow to thaw </t>
+          <t>½ tsp chilli powder</t>
         </is>
       </c>
       <c r="F26" s="2" t="n"/>
@@ -3541,7 +3373,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bell pepper</t>
+          <t>flour</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3549,17 +3381,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bell Pepper Red</t>
+          <t>All Purpose Flour (Maida)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bell Pepper Orange, Bell Pepper Yellow</t>
+          <t>Almond Flour, Bread Flour, Cake Flour, Coconut Flour, Oat Flour, Rice Flour, Self Raising Flour, Tapioca Flour</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1 bell pepper, cubed ( i used a mix of green, yellow and red )</t>
+          <t>2 tbsp flour</t>
         </is>
       </c>
       <c r="F27" s="2" t="n"/>
@@ -3567,7 +3399,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>paprika</t>
+          <t>sourdough</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -3575,17 +3407,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Smoked Paprika</t>
+          <t>Sourdough Slices</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sweet Paprika</t>
+          <t>Sourdough Loaf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1 tsp paprika</t>
+          <t>2 slices sourdough, toasted</t>
         </is>
       </c>
       <c r="F28" s="2" t="n"/>
@@ -3593,7 +3425,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chilli powder</t>
+          <t>coconut</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3601,17 +3433,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Red Chilli Powder</t>
+          <t>Desiccated Coconut</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Kashmiri Chilli Powder</t>
+          <t>Coconut Chips, Coconut Cream, Coconut Flour, Coconut Milk, Coconut Sugar, Dry Coconut (Copra), Virgin Coconut Oil</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>½ tsp chilli powder</t>
+          <t>2 tbsp grated coconut</t>
         </is>
       </c>
       <c r="F29" s="2" t="n"/>
@@ -3619,7 +3451,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>flour</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3627,17 +3459,13 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>All Purpose Flour (Maida)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Almond Flour, Bread Flour, Cake Flour, Coconut Flour, Oat Flour, Rice Flour, Self Raising Flour, Tapioca Flour</t>
-        </is>
-      </c>
+          <t>Curd</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2 tbsp flour</t>
+          <t>1 tbsp yogurt</t>
         </is>
       </c>
       <c r="F30" s="2" t="n"/>
@@ -3645,25 +3473,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>coconut</t>
+          <t>parmesan cheese</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Desiccated Coconut</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Coconut Chips, Coconut Cream, Coconut Flour, Coconut Milk, Coconut Sugar, Dry Coconut (Copra), Virgin Coconut Oil</t>
-        </is>
-      </c>
+          <t>Parmesan</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2 tbsp grated coconut</t>
+          <t>1/4 cup grated Parmesan cheese</t>
         </is>
       </c>
       <c r="F31" s="2" t="n"/>
@@ -3671,21 +3495,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yogurt</t>
+          <t>mango</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Curd</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Frozen Mango Chunks</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Raw Mango</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1 tbsp yogurt</t>
+          <t>1 whole mango, i use alphonso</t>
         </is>
       </c>
       <c r="F32" s="2" t="n"/>
@@ -3693,25 +3521,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nuts</t>
+          <t>mozarella cheese</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(none yet)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>macadamia nuts, pine nuts</t>
-        </is>
-      </c>
+          <t>Mozzarella</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>nuts, seeds, candy, whatever your heart desires :)</t>
+          <t>25 grams mozarella cheese</t>
         </is>
       </c>
       <c r="F33" s="2" t="n"/>
@@ -3719,25 +3543,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sauce</t>
+          <t>chili</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(none yet)</t>
+          <t>Green Chilli</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>arrabbiata sauce, bbq sauce, burger sauce, fish sauce, hoisin sauce</t>
+          <t>Chili Oil, Chilli Garlic Sauce, Green Chilli Sauce, Kashmiri Chilli Powder, Red Chilli Powder, Red Chilli Sauce, Sweet Chilli Sauce</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>sauce</t>
+          <t>1 chili, finely chopped</t>
         </is>
       </c>
       <c r="F34" s="2" t="n"/>
@@ -3745,11 +3569,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dressing</t>
+          <t>boneless</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3758,12 +3582,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>balsamic dressing, caesar dressing, ranch dressing, thousand island dressing</t>
+          <t>chicken breast boneless, chicken thigh boneless</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>dressing</t>
+          <t>2 boneless, skinless chicken breasts</t>
         </is>
       </c>
       <c r="F35" s="2" t="n"/>
@@ -3771,11 +3595,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>lettuce</t>
+          <t>ginger garlic</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3784,12 +3608,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>lettuce iceberg, romaine lettuce</t>
+          <t>garlic, ginger</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chopped lettuce</t>
+          <t>1 tbsp minced ginger and garlic</t>
         </is>
       </c>
       <c r="F36" s="2" t="n"/>
@@ -3797,7 +3621,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>parmesan cheese</t>
+          <t>sweetener</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -3805,13 +3629,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Parmesan</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>(none yet)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>erythritol sweetener, stevia sweetener</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1/4 cup grated Parmesan cheese</t>
+          <t>1 tbsp sweetener ( honey/ maple syrup/sugar )</t>
         </is>
       </c>
       <c r="F37" s="2" t="n"/>
@@ -3819,7 +3647,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mozarella cheese</t>
+          <t>raisins</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -3827,13 +3655,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mozzarella</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>(none yet)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>black raisins, raisins (golden)</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>25 grams mozarella cheese</t>
+          <t>1 tbsp raisins</t>
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
@@ -3841,7 +3673,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>chili</t>
+          <t>dark chocolate chunks</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -3849,17 +3681,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Green Chilli</t>
+          <t>(none yet)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chili Oil, Chilli Garlic Sauce, Green Chilli Sauce, Kashmiri Chilli Powder, Red Chilli Powder, Red Chilli Sauce, Sweet Chilli Sauce</t>
+          <t>dark chocolate (55%), dark chocolate (70%)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1 chili, finely chopped</t>
+          <t>150 grams dark chocolate chunks</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
@@ -3867,7 +3699,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>boneless</t>
+          <t>honey corn syrup glucose</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -3880,12 +3712,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>chicken breast boneless, chicken thigh boneless</t>
+          <t>honey, corn</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2 boneless, skinless chicken breasts</t>
+          <t>35 grams honey or corn syrup or glucose ( when using honey, your honey</t>
         </is>
       </c>
       <c r="F40" s="2" t="n"/>
@@ -3893,7 +3725,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ginger garlic</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -3906,12 +3738,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>garlic, ginger</t>
+          <t>dark chocolate (55%), dark chocolate (70%), soy sauce (dark)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1 tbsp minced ginger and garlic</t>
+          <t>150 grams dark / milk chocolate, if enrobing</t>
         </is>
       </c>
       <c r="F41" s="2" t="n"/>
@@ -3919,7 +3751,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sweetener</t>
+          <t>square dark chocolate</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -3932,12 +3764,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>erythritol sweetener, stevia sweetener</t>
+          <t>dark chocolate (55%), dark chocolate (70%)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1 tbsp sweetener ( honey/ maple syrup/sugar )</t>
+          <t>1 square dark chocolate if you want it to be extract chocolatelyyy &lt;3</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
@@ -3945,7 +3777,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>raisins</t>
+          <t>dark chocolate cube</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -3958,12 +3790,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>black raisins, raisins (golden)</t>
+          <t>dark chocolate (55%), dark chocolate (70%)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1 tbsp raisins</t>
+          <t>70% dark chocolate cube</t>
         </is>
       </c>
       <c r="F43" s="2" t="n"/>
@@ -3971,7 +3803,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>masala</t>
+          <t>light soy sauce tsp dark soy</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -3984,12 +3816,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>biryani masala, chaat masala, chicken masala, chole masala, garam masala</t>
+          <t>soy sauce (dark), soy sauce (light)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>masala</t>
+          <t>1/2 tbsp light soy sauce or 1/2 tsp dark soy</t>
         </is>
       </c>
       <c r="F44" s="2" t="n"/>
@@ -3997,7 +3829,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>i used grams hersheys creamy milk chocolate grams callebautindia chips because dark chocolate is better always</t>
+          <t>mangoes</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -4010,12 +3842,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>chocolate chips, dark chocolate (55%), dark chocolate (70%), milk chocolate</t>
+          <t>raw mango, frozen mango chunks</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>i used 75 grams of hersheys creamy milk chocolate and 25 grams of @cal</t>
+          <t>2 - 3 mangoes, peeled and cubed</t>
         </is>
       </c>
       <c r="F45" s="2" t="n"/>
@@ -4023,7 +3855,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dark chocolate chunks</t>
+          <t>kashmiri red chilli powder</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -4036,12 +3868,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>dark chocolate (55%), dark chocolate (70%)</t>
+          <t>kashmiri chilli powder, red chilli powder</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>150 grams dark chocolate chunks</t>
+          <t>1 tbsp Kashmiri red chilli powder</t>
         </is>
       </c>
       <c r="F46" s="2" t="n"/>
@@ -4049,7 +3881,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>paste</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -4062,12 +3894,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>harissa paste, tomato paste, vanilla bean paste, thai green curry paste, thai red curry paste</t>
+          <t>chicken masala, chicken breast boneless, chicken mince (keema), chicken thigh boneless, butter chicken masala</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>paste</t>
+          <t>450 grams chicken, cut into small cubes</t>
         </is>
       </c>
       <c r="F47" s="2" t="n"/>
@@ -4075,7 +3907,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>honey corn syrup glucose</t>
+          <t>egg white</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -4088,12 +3920,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>honey, corn</t>
+          <t>egg whites, white eggs</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>35 grams honey or corn syrup or glucose ( when using honey, your honey</t>
+          <t>1 egg white</t>
         </is>
       </c>
       <c r="F48" s="2" t="n"/>
@@ -4101,7 +3933,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>cloves garlic</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -4114,12 +3946,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>dark chocolate (55%), dark chocolate (70%), soy sauce (dark)</t>
+          <t>cloves, garlic</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>150 grams dark / milk chocolate, if enrobing</t>
+          <t>1 2 cloves of garlic</t>
         </is>
       </c>
       <c r="F49" s="2" t="n"/>
@@ -4127,7 +3959,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>square dark chocolate</t>
+          <t>almond</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -4140,12 +3972,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>dark chocolate (55%), dark chocolate (70%)</t>
+          <t>almond flour, almond flakes, almond slivers, almonds (whole), almond butter</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1 square dark chocolate if you want it to be extract chocolatelyyy &lt;3</t>
+          <t>200 ml almond / oats milk</t>
         </is>
       </c>
       <c r="F50" s="2" t="n"/>
@@ -4153,7 +3985,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dark chocolate cube</t>
+          <t>lettuce</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -4166,12 +3998,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>dark chocolate (55%), dark chocolate (70%)</t>
+          <t>lettuce iceberg, romaine lettuce</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>70% dark chocolate cube</t>
+          <t>1 lettuce, hand shredded</t>
         </is>
       </c>
       <c r="F51" s="2" t="n"/>
@@ -4179,7 +4011,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>light soy sauce tsp dark soy</t>
+          <t>chilli sauce</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -4192,12 +4024,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>soy sauce (dark), soy sauce (light)</t>
+          <t>chilli garlic sauce, green chilli sauce, red chilli sauce, sweet chilli sauce</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1/2 tbsp light soy sauce or 1/2 tsp dark soy</t>
+          <t>1 tbsp chilli sauce</t>
         </is>
       </c>
       <c r="F52" s="2" t="n"/>
@@ -4205,7 +4037,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>mangoes</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -4218,12 +4050,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>raw mango, frozen mango chunks</t>
+          <t>soy sauce (dark), soy sauce (light)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2 - 3 mangoes, peeled and cubed</t>
+          <t>1/2 tbsp soy</t>
         </is>
       </c>
       <c r="F53" s="2" t="n"/>
@@ -4231,7 +4063,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kashmiri red chilli powder</t>
+          <t>green</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -4244,12 +4076,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>kashmiri chilli powder, red chilli powder</t>
+          <t>green peas, green olives, green cardamom, capsicum green, green beans</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1 tbsp Kashmiri red chilli powder</t>
+          <t>1 green / red capsicum, sliced</t>
         </is>
       </c>
       <c r="F54" s="2" t="n"/>
@@ -4257,7 +4089,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>curry paste</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -4270,12 +4102,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>chicken masala, chicken breast boneless, chicken mince (keema), chicken thigh boneless, butter chicken masala</t>
+          <t>thai green curry paste, thai red curry paste, thai yellow curry paste</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>450 grams chicken, cut into small cubes</t>
+          <t>1 - 1.5 tbsp curry paste, depends on how strong your paste is in flavo</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
@@ -4283,7 +4115,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>egg white</t>
+          <t>shallots onions</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -4296,12 +4128,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>egg whites, white eggs</t>
+          <t>onion, shallots</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1 egg white</t>
+          <t>100 grams shallots or 2 sliced onions</t>
         </is>
       </c>
       <c r="F56" s="2" t="n"/>
@@ -4309,7 +4141,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>cloves garlic</t>
+          <t>coriander leaves &amp; cup dill</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -4322,223 +4154,15 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>cloves, garlic</t>
+          <t>coriander, dill</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1 2 cloves of garlic</t>
+          <t>1/2 cup of coriander leaves &amp; 1/2 cup dill</t>
         </is>
       </c>
       <c r="F57" s="2" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>almond</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>(none yet)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>almond flour, almond flakes, almond slivers, almonds (whole), almond butter</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>200 ml almond / oats milk</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>chilli sauce</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>(none yet)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>chilli garlic sauce, green chilli sauce, red chilli sauce, sweet chilli sauce</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>1 tbsp chilli sauce</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>soy</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>(none yet)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>soy sauce (dark), soy sauce (light)</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1/2 tbsp soy</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>(none yet)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>green peas, green olives, green cardamom, capsicum green, green beans</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>1 green / red capsicum, sliced</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>curry paste</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>(none yet)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>thai green curry paste, thai red curry paste, thai yellow curry paste</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1 - 1.5 tbsp curry paste, depends on how strong your paste is in flavo</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>sprinkle parmesan</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>(none yet)</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>parmesan, sprinkles</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>sprinkle of parmesan, to top</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>shallots onions</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>(none yet)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>onion, shallots</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>100 grams shallots or 2 sliced onions</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>coriander leaves &amp; cup dill</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>(none yet)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>coriander, dill</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>1/2 cup of coriander leaves &amp; 1/2 cup dill</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4551,7 +4175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4597,34 +4221,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cheese Block</t>
+          <t>Cinnamon Sticks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>grated cheese</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>1/2 inch cinnamon</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2 g each</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Caesar Dressing</t>
+          <t>Jalapeños</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4632,7 +4260,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Caesar dressing</t>
+          <t>5-6 jalapeños, chopped</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -4641,7 +4269,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cinnamon Sticks</t>
+          <t>Dark Chocolate (55%)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4650,24 +4278,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1/2 inch cinnamon</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2 g each</t>
-        </is>
-      </c>
+          <t>2-3 pieces ( 15 grams ) of dark chocolate, melted ( i used bournville 70% )</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jalapeños</t>
+          <t>Bay Leaves</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4676,11 +4300,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5-6 jalapeños, chopped</t>
+          <t>1 bay leaf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -4689,72 +4313,64 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Sourdough Slices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>unit "slice"</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sliced tomatoes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>100 g each</t>
-        </is>
-      </c>
+          <t>2 slices sourdough, toasted</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Onion</t>
+          <t>Cashews (Whole)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>spring onion + white sesame seeds</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>110 g each</t>
-        </is>
-      </c>
+          <t>15 cashews</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cocoa Powder</t>
+          <t>Beetroot</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OR 1 tbsp cocoa powder + water + 1 tsp monkfruit to create a paste</t>
+          <t>4 beetroots, washed, peeled and cubed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -4763,7 +4379,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dark Chocolate (55%)</t>
+          <t>Basil</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4772,11 +4388,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2-3 pieces ( 15 grams ) of dark chocolate, melted ( i used bournville 70% )</t>
+          <t>10 basil leaves, sliced thin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -4785,72 +4401,64 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Garlic</t>
+          <t>Cheese Block</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>minced garlic</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4 g each</t>
-        </is>
-      </c>
+          <t>½ slice cheese</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cucumber</t>
+          <t>Romaine Lettuce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cucumber salsa</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>200 g each</t>
-        </is>
-      </c>
+          <t>1 large head romaine lettuce, chopped</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vanilla Extract</t>
+          <t>Cheese Cubes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>few drops of vanilla extract</t>
+          <t>2 cheese cubes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -4859,7 +4467,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bay Leaves</t>
+          <t>Puff Pastry Sheets</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4868,11 +4476,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1 bay leaf</t>
+          <t xml:space="preserve">1 sheet puff pastry, thawed in the fridge overnight is best, I took mine out to </t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -4881,20 +4489,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salted Butter</t>
+          <t>Cornstarch</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>butter + caster sugar for buttering and dusting the ramekin</t>
+          <t>1 /2 tbsp cornflour / arrow root powder</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -4903,46 +4511,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Kashmiri Chilli Powder</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>grated carrot, optional</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>70 g each</t>
-        </is>
-      </c>
+          <t>8 kashmiri chilli</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ghee</t>
+          <t>Cloves</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>knobb of ghee</t>
+          <t>2 - 3 cardamom cloves</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -4951,20 +4555,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sourdough Slices</t>
+          <t>Frozen Mango Chunks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>unit "slice"</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2 slices sourdough, toasted</t>
+          <t>1 whole mango, i use alphonso</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -4973,7 +4577,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cashews (Whole)</t>
+          <t>Shallots</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4982,11 +4586,11 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15 cashews</t>
+          <t>8-10 shallots</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -4995,12 +4599,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Frozen Mango Chunks</t>
+          <t>Turmeric Powder</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>recipe gives no quantity</t>
+          <t>need grams per piece</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -5008,893 +4612,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mango, i use frozen mangoes that i keep in the freezer, allow to thaw for 10 min</t>
+          <t>1/2 turmeric powder</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Beetroot</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>4 beetroots, washed, peeled and cubed</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Basil</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>10 basil leaves, sliced thin</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>White Eggs</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>egg + crumb coating</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Cheese Slices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>cheese slices</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>20 g each</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Desiccated Coconut</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>dessicated coconut</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Parmesan</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Extra Parmesan</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cheese Block</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>½ slice cheese</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Tomato Ketchup</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Ketchup + yellow mustard (non negotiable!)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>100 g each</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Jalapeños</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Jalapeños + red paprika</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Dijon Mustard</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Mustard + ketchup, as desired</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Romaine Lettuce</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1 large head romaine lettuce, chopped</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Cheese Cubes</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2 cheese cubes</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Tomato Paste</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>cashew tomato paste: 8 cashews + 2 tomato</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>100 g each</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Hakka Noodles</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Noodles + greens</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Puff Pastry Sheets</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 sheet puff pastry, thawed in the fridge overnight is best, I took mine out to </t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Cornstarch</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1 /2 tbsp cornflour / arrow root powder</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Kashmiri Chilli Powder</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>8 kashmiri chilli</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Pav</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Whole wheat pav</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Granola</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>crunchy granola, optional, for crunch</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" s="2" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Sourdough Slices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>toasted sourdough</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Cloves</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2 - 3 cardamom cloves</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Frozen Mango Chunks</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1 whole mango, i use alphonso</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" s="2" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Red Onion</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>pickled red onions (recipe is on my paneer roll reel)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>110 g each</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Olive Oil Spray</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Few sprays of olive oil, optional</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" s="2" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Shallots</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>8-10 shallots</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Sprinkles</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>sprinkle of salt</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Bell Pepper Red</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Red bell pepper, optional, sliced</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>150 g each</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Evaporated Milk</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>evaporated milk - 177 ml ( boil 350 ml of milk for 20 minutes till it reduced to</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" s="2" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Condensed Milk</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>condensed milk - 200 ml</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" s="2" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Toned Milk</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>milk - 60 ml</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" s="2" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Whipping Cream</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>heavy whipping cream - 60 - 80 ml ( DO NOT USE AMUL CREAM)</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" s="2" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Turmeric Powder</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>need grams per piece</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1/2 turmeric powder</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" s="2" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Ricotta</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Ricotta</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Spinach</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Spinach</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Mozzarella</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Mozzarella</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" s="2" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Paneer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Paneer &amp; vegetables</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Groundnut Oil</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Oil</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" s="2" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Whole Wheat Bread</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>brown bread croutons</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>30 g each</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Chocolate Chips</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>recipe gives no quantity</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>vegan chocolate chips / shavings + biscuit crumbs</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5907,7 +4629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5935,30 +4657,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>knobb butter</t>
+          <t>pasta choice</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>knobb of butter</t>
+          <t>100 grams pasta of choice</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>marinade</t>
+          <t>apples</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marinade - you can play around with the spices as per your preference of flavours</t>
+          <t>2 apples, peeled and cubed</t>
         </is>
       </c>
     </row>
@@ -5969,7 +4691,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5980,22 +4702,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pasta choice</t>
+          <t>cheese choice</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>100 grams pasta of choice</t>
+          <t>25 grams cheese of choice, i use amul</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>spices</t>
+          <t>pickles</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6003,14 +4725,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spices ( you can add more basis your personal preference keeping in mind that marinades dilute flavours)</t>
+          <t>2 - 3 pickles (gerkin) diced</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>boiling water</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6018,14 +4740,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2 apples, peeled and cubed</t>
+          <t>1/2 cup boiling water</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a handful cashew nuts</t>
+          <t>gochugara any chilli flakes</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6033,14 +4755,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>a handful of cashew nuts</t>
+          <t>1 tbsp gochugara or any chilli flakes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cheese choice</t>
+          <t>box</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6048,119 +4770,119 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25 grams cheese of choice, i use amul</t>
+          <t>1 box / 200 grams buttom mushroom</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pickles</t>
+          <t>block chocolate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2 - 3 pickles (gerkin) diced</t>
+          <t>1 small block of chocolate, i used 70% sugar free but use any chocolate you want, calories wont vary that much</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>boiling water</t>
+          <t>chicken breast thigh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1/2 cup boiling water</t>
+          <t>450 grams chicken breast or thigh, cubed | use paneer for vegetarian option</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>salt &amp; pepper</t>
+          <t>oregano chilli flakes each</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt &amp; pepper (to your liking)</t>
+          <t>2 packets of oregano and chilli flakes each, i use dominoes ;)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gochugara any chilli flakes</t>
+          <t>peri peri sprinkle after cooking</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1 tbsp gochugara or any chilli flakes</t>
+          <t>1 tsp peri peri to sprinkle after cooking</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>any vegetables</t>
+          <t>oil fry bhindi</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>any vegetables you want</t>
+          <t>1.5 tbsp oil to fry the bhindi</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tikka marinade</t>
+          <t>milk choice</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tikka Marinade - marinate paneer for 30 minutes minimum</t>
+          <t>60 ml milk of choice</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>chocolate pieces</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1 box / 200 grams buttom mushroom</t>
+          <t>2-3 chocolate pieces</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>block chocolate</t>
+          <t>butter oil</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6168,14 +4890,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1 small block of chocolate, i used 70% sugar free but use any chocolate you want, calories wont vary that much</t>
+          <t>1 tbsp butter or oil</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>your favourite vegetables choice</t>
+          <t>yolk</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6183,14 +4905,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Your favourite vegetables of choice</t>
+          <t>1 yolk ( use the extra white for breakfast)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chicken breast thigh</t>
+          <t>pita pockets</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6198,14 +4920,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>450 grams chicken breast or thigh, cubed | use paneer for vegetarian option</t>
+          <t>6 pita pockets / 4 rotis / bread works good too</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a few drops vanilla extract</t>
+          <t>canned jalapenos</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6213,14 +4935,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>a few drops of vanilla extract, optional</t>
+          <t>50-70 grams canned jalapenos, i used both green and red</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>oregano chilli flakes each</t>
+          <t>pasta speghetti</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6228,14 +4950,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2 packets of oregano and chilli flakes each, i use dominoes ;)</t>
+          <t>120 grams pasta speghetti ( perfect quantity for 2 people) ( i use barilla whole wheat)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>slurry</t>
+          <t>pickle</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6243,14 +4965,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>slurry - 1 tsp cornflour + 3 tbsp water</t>
+          <t>2 pickle (gerkin) diced</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>but</t>
+          <t>idli dosa batter</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6258,14 +4980,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>but you will need to add in some salt + pepper</t>
+          <t>80 grams idli/dosa batter</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>peri peri sprinkle after cooking</t>
+          <t>relish per burger</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6273,14 +4995,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1 tsp peri peri to sprinkle after cooking</t>
+          <t>1 tsp relish per burger</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cheats mayo</t>
+          <t>hung curd whipped spice masalas</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6288,14 +5010,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cheats “mayo”</t>
+          <t>1 - 2 tbsp of hung curd whipped to cut the spice and masalas :)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oil fry bhindi</t>
+          <t>cream tartare</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6303,14 +5025,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.5 tbsp oil to fry the bhindi</t>
+          <t>pinch of cream of tartare, skip if you do not have</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>milk choice</t>
+          <t>reserved water from pressure cooker</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6318,14 +5040,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>60 ml milk of choice</t>
+          <t>1-1.5 cup reserved water from the pressure cooker</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>topping</t>
+          <t>biscuits</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6333,14 +5055,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>topping</t>
+          <t>25 grams crushed biscuits</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chocolate pieces</t>
+          <t>tinned san marzano tomatoes</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6348,14 +5070,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2-3 chocolate pieces</t>
+          <t>400g tinned San Marzano tomatoes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>butter oil</t>
+          <t>cup amul cream</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6363,14 +5085,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1 tbsp butter or oil</t>
+          <t>2 tbsp - 1/4 cup amul cream, adjust for consistency</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yolk</t>
+          <t>salt more</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6378,14 +5100,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1 yolk ( use the extra white for breakfast)</t>
+          <t>1 tsp salt or more as needed</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>add as many as little chocolate chips</t>
+          <t>leftover dal</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6393,14 +5115,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>add as many or as little chocolate chips you want</t>
+          <t>150 grams leftover dal , i use this amount as my dal is quite thick, if using a thinner dal, you need to adjus</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dip</t>
+          <t>licious foods chicken mince</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6408,14 +5130,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dip</t>
+          <t>450g @licious_foods chicken mince</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pita pockets</t>
+          <t>chicken kheema paneer bhurji would be tasty tooo</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6423,14 +5145,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6 pita pockets / 4 rotis / bread works good too</t>
+          <t>120 grams chicken kheema ( recipe in my chicken kheema dosa recipe) | paneer bhurji would be tasty tooo</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>canned jalapenos</t>
+          <t>coriander with stems</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6438,14 +5160,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>50-70 grams canned jalapenos, i used both green and red</t>
+          <t>handful of coriander with stems</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pasta speghetti</t>
+          <t>softboiled egg</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6453,14 +5175,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>120 grams pasta speghetti ( perfect quantity for 2 people) ( i use barilla whole wheat)</t>
+          <t>2 softboiled egg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>as is with toast</t>
+          <t>chicken breast thighs</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6468,14 +5190,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>as is or with toast</t>
+          <t>450g chicken breast or thighs, cut into bite-sized pieces</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mince</t>
+          <t>bread slices</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6483,14 +5205,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mince</t>
+          <t>2 bread slices, i use whole wheat</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>reserve water from cooking maggi</t>
+          <t>water thin consistency</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6498,14 +5220,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>reserve water from cooking the maggi</t>
+          <t>1 - 2 tbsp water to thin consistency</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>you can also add any other veges</t>
+          <t>uncooked pasta per</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6513,14 +5235,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>you can also add any other veges you want!!!!</t>
+          <t>45 grams of uncooked pasta per serving</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>per sandwich</t>
+          <t>olive sesame oil saute paneer</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6528,14 +5250,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Per sandwich</t>
+          <t>1 tsp olive/sesame oil to saute paneer</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>chicken steak</t>
+          <t>oil cook base</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6543,14 +5265,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicken Steak</t>
+          <t>1/2 tsp oil to cook base</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pickle</t>
+          <t>coffee</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6558,14 +5280,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2 pickle (gerkin) diced</t>
+          <t>1 tbsp coffee</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>idli dosa batter</t>
+          <t>fat</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6573,14 +5295,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>80 grams idli/dosa batter</t>
+          <t>1 - 1.5 cups whole fat / slim milk</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>relish per burger</t>
+          <t>sugar stevia jaggery</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6588,14 +5310,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 tsp relish per burger</t>
+          <t>1 tsp sugar/stevia/jaggery</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hung curd whipped spice masalas</t>
+          <t>chocolate callets</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6603,14 +5325,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 - 2 tbsp of hung curd whipped to cut the spice and masalas :)</t>
+          <t>5-6 chocolate callets</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cream tartare</t>
+          <t>smoked chilli jaggery sauce</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6618,14 +5340,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>pinch of cream of tartare, skip if you do not have</t>
+          <t>1 tbsp smoked chilli jaggery sauce</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gravy</t>
+          <t>stalk spring onion greens</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6633,14 +5355,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>gravy</t>
+          <t>1 stalk spring onion greens, chopped</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>reserved water from pressure cooker</t>
+          <t>ginger paste a piece ginger</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -6648,14 +5370,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1-1.5 cup reserved water from the pressure cooker</t>
+          <t>1 tsp ginger paste or a small piece of ginger</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>biscuits</t>
+          <t>coriander leaves cup water blend</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -6663,14 +5385,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>25 grams crushed biscuits</t>
+          <t>Handful of coriander leaves and 1/4 cup water to blend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tinned san marzano tomatoes</t>
+          <t>sesame oil olive oil</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -6678,14 +5400,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>400g tinned San Marzano tomatoes</t>
+          <t>1 tsp sesame oil or olive oil</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>a little parmesan cheese</t>
+          <t>honey top with after cooking</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -6693,14 +5415,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>a little grated parmesan cheese</t>
+          <t>1 tsp honey to top with after cooking ( as many people believe you should not heat honey but the flavour is ba</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cup amul cream</t>
+          <t>spring onion green</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -6708,14 +5430,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2 tbsp - 1/4 cup amul cream, adjust for consistency</t>
+          <t>1 spring onion green, chopped</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>nobb butter</t>
+          <t>white rice</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -6723,14 +5445,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nobb of butter</t>
+          <t>1 cup cooked white rice</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tadka cook</t>
+          <t>rice noodles any your prefered noodles</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -6738,14 +5460,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>tadka to cook</t>
+          <t>120 grams rice noodles or any of your prefered noodles</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>serve</t>
+          <t>dry pasta</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -6753,14 +5475,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>to serve, 1 tsp ghee</t>
+          <t>2 cups dry pasta, cooked</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>salt more</t>
+          <t>leftover rice</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -6768,14 +5490,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1 tsp salt or more as needed</t>
+          <t>2-3 cups cooked leftover rice that has been in the fridge for atleast 12 hours</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>i forgot add coriander</t>
+          <t>cardamom pods</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -6783,14 +5505,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>i forgot to add coriander, but you should definately add some :)</t>
+          <t>3 cardamom pods, green</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>leftover dal</t>
+          <t>oil tbsp oil</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -6798,14 +5520,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>150 grams leftover dal , i use this amount as my dal is quite thick, if using a thinner dal, you need to adjus</t>
+          <t>2 tbsp oil or 1 tbsp oil</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>licious foods chicken mince</t>
+          <t>granola per serve</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -6813,14 +5535,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>450g @licious_foods chicken mince</t>
+          <t>2 tbsp granola per serve for crunch and flavour</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>chicken kheema paneer bhurji would be tasty tooo</t>
+          <t>mango per serve</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -6828,14 +5550,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>120 grams chicken kheema ( recipe in my chicken kheema dosa recipe) | paneer bhurji would be tasty tooo</t>
+          <t>1 tbsp chopped mango per serve</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>coriander with stems</t>
+          <t>aqua</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -6843,14 +5565,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>handful of coriander with stems</t>
+          <t>1/4 cup aqua</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>a pinch turmeric</t>
+          <t>cheese slice cheese is always subjective in a recipe</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -6858,14 +5580,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>a pinch of turmeric</t>
+          <t xml:space="preserve">1 cheese slice ( you can use grated cheese as well) Cheese is always subjective in a recipe, add as little or </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>softboiled egg</t>
+          <t>milk balance consistency</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -6873,14 +5595,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2 softboiled egg</t>
+          <t>2-3 tbsp milk to balance consistency</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>chicken breast thighs</t>
+          <t>pita per bowl salad</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6888,14 +5610,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>450g chicken breast or thighs, cut into bite-sized pieces</t>
+          <t>1/2 pita per bowl of salad cut into 4 triangles, airfried for 5 minutes till golden brown and crisp</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bread slices</t>
+          <t>mixed with tbsp water</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -6903,14 +5625,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2 bread slices, i use whole wheat</t>
+          <t>1/2 tbsp mixed with 2 tbsp water</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>water thin consistency</t>
+          <t>rcp</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6918,14 +5640,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1 - 2 tbsp water to thin consistency</t>
+          <t>1 tbsp RCP</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>temper</t>
+          <t>peri peri seasoning tbsp cajun seasoning is great toooo</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -6933,14 +5655,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>temper</t>
+          <t>1 tbsp peri peri seasoning or 1 tbsp cajun seasoning is great toooo</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>uncooked pasta per</t>
+          <t>grounud black pepper</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -6948,14 +5670,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>45 grams of uncooked pasta per serving</t>
+          <t>1 tsp grounud black pepper</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>olive sesame oil saute paneer</t>
+          <t>low fat paneer</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -6963,14 +5685,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1 tsp olive/sesame oil to saute paneer</t>
+          <t>200 grams low fat paneer, grated</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>oil cook base</t>
+          <t>ghee per paratha</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -6978,14 +5700,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1/2 tsp oil to cook base</t>
+          <t>1 tsp ghee per paratha while cooking on tava</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>toppings</t>
+          <t>salt salted caramel</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -6993,14 +5715,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>toppings</t>
+          <t>pinch of salt = salted caramel</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>coffee</t>
+          <t>tbsp milk</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -7008,14 +5730,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1 tbsp coffee</t>
+          <t>1 . 5 tbsp milk</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>fat</t>
+          <t>pasta per person</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -7023,14 +5745,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1 - 1.5 cups whole fat / slim milk</t>
+          <t>50-60 grams pasta per person for a hearty meal, can be customized as per your preference</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>having a frother is amazing</t>
+          <t>packed cup spinach</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -7038,14 +5760,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Having a frother is amazing but if you don’t a spoon works fine!</t>
+          <t>1 packed cup spinach</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sugar stevia jaggery</t>
+          <t>milk water</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -7053,14 +5775,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1 tsp sugar/stevia/jaggery</t>
+          <t>1 tbsp milk/water (optional, for softer eggs)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>chocolate callets</t>
+          <t>olive oil butter</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -7068,14 +5790,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>5-6 chocolate callets</t>
+          <t>1/2 tsp olive oil or butter</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>smoked chilli jaggery sauce</t>
+          <t>cornflour mixed with tbsp milk</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -7083,14 +5805,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1 tbsp smoked chilli jaggery sauce</t>
+          <t>1/2 tsp cornflour mixed with 1 tbsp milk, optional but gives a thicker cup</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>stalk spring onion greens</t>
+          <t>water grind</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -7098,14 +5820,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1 stalk spring onion greens, chopped</t>
+          <t>3 tbsp water to grind</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>coconut slushy</t>
+          <t>chicken marinated with tsp gochujang paste</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -7113,14 +5835,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>coconut slushy</t>
+          <t>200 grams chicken marinated with 1/2 tsp gochujang paste</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ginger paste a piece ginger</t>
+          <t>rice flour mixed with cup water</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -7128,980 +5850,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1 tsp ginger paste or a small piece of ginger</t>
+          <t>1 tbsp rice flour mixed with 1/4 cup water</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>coriander leaves cup water blend</t>
+          <t>boombayway vegan garlic mayo</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
-        <is>
-          <t>Handful of coriander leaves and 1/4 cup water to blend</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>sesame oil olive oil</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1 tsp sesame oil or olive oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>honey top with after cooking</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1 tsp honey to top with after cooking ( as many people believe you should not heat honey but the flavour is ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>spring onion green</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1 spring onion green, chopped</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>white rice</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1 cup cooked white rice</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>rice noodles any your prefered noodles</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>120 grams rice noodles or any of your prefered noodles</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>dry pasta</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2 cups dry pasta, cooked</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>add whatever veggies</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Add whatever veggies you like—TBH, I kept it simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>leftover rice</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2-3 cups cooked leftover rice that has been in the fridge for atleast 12 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>half packet</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>extra half packet, maggi masala</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>cardamom pods</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>3 cardamom pods, green</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>oil tbsp oil</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2 tbsp oil or 1 tbsp oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>mango pieces</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>fresh cut mango pieces for topping</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>next morning</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>the next morning, layer with fresh mango and serve :)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>granola per serve</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2 tbsp granola per serve for crunch and flavour</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>mango per serve</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>1 tbsp chopped mango per serve</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>vegetables vegetables maximum else reduce quantities each</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Optional vegetables: 2 vegetables maximum else reduce quantities of each</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>aqua</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1/4 cup aqua</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>additional grams whipped cream gives a light airy ganache</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>additional 30 grams of whipped cream gives a light and airy ganache for the topping</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>cheese slice cheese is always subjective in a recipe</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 cheese slice ( you can use grated cheese as well) Cheese is always subjective in a recipe, add as little or </t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>increase protein in meal by adding chicken</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Increase protein in the meal by adding -cooked chicken, paneer, tofu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>milk balance consistency</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>1</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2-3 tbsp milk to balance consistency</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>pressure cooker base</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>1</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Pressure Cooker Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>assembly</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>assembly</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>pita per bowl salad</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>1</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>1/2 pita per bowl of salad cut into 4 triangles, airfried for 5 minutes till golden brown and crisp</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>mixed with tbsp water</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>1</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>1/2 tbsp mixed with 2 tbsp water</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>bunch coriander leaves</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>large bunch of coriander leaves + some stems wont matter as it will be blended</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>assemble</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>1</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>to assemble,</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>any other vegetables choice</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>1</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>any other vegetables of choice</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>rcp</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>1</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>1 tbsp RCP</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>pav slider buns</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>1</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Pav or slider buns</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>peri peri seasoning tbsp cajun seasoning is great toooo</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>1</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>1 tbsp peri peri seasoning or 1 tbsp cajun seasoning is great toooo</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>season with salt</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>1</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>season with salt + pepper + any spices you want! Adds flavour</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>a little butter fry french toast</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>1</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>a little butter to fry the french toast</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>a few sprigs coriander leaves</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>1</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>a few sprigs of coriander leaves</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>grounud black pepper</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>1</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>1 tsp grounud black pepper</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>serve as is with a slice toast</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>1</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>serve as is or with a slice of toast</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ml water</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>1</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>around 400 ml water, should completely submerge</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>low fat paneer</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>1</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>200 grams low fat paneer, grated</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>roti dough made with wheat flour</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>1</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>regular roti dough made with whole wheat flour</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>ghee per paratha</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>1</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>1 tsp ghee per paratha while cooking on tava</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>sponge cake</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>1</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>sponge cake - 1 portion (recipe in the previous reel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>tadka</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>1</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>tadka</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>salt salted caramel</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>1</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>pinch of salt = salted caramel</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>serves one</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Serves one, double/triple the recipe for more people</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>tbsp milk</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>1</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>1 . 5 tbsp milk</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>pasta per person</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>1</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>50-60 grams pasta per person for a hearty meal, can be customized as per your preference</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>packed cup spinach</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>1</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>1 packed cup spinach</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>milk water</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>1</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>1 tbsp milk/water (optional, for softer eggs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>olive oil butter</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>1</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>1/2 tsp olive oil or butter</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>keeps well in fridge</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>1</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>keeps well in the fridge for 2-3 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>tomato pasta sauce</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>1</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Tomato pasta sauce</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>cornflour mixed with tbsp milk</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>1/2 tsp cornflour mixed with 1 tbsp milk, optional but gives a thicker cup</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>a few pieces brocolli florettes</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>a few pieces of brocolli florettes, blanched and cooled</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>sweet &amp; sour sauce</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Sweet &amp; sour sauce ( feel free to adjust as per your taste - more/less spicy/salty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>coconut curry sauce</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Coconut curry sauce</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>you can</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>you can use walnuts, hazelnuts, pistachios etc as per your preference :)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>water grind</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>3 tbsp water to grind</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>cool this blend it</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>cool this and blend it into a smooth paste</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>time make tadka</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>time to make the tadka,</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>a handful bunch coriander</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>a handful bunch of coriander</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>reduce quantity chocolate add nuts your choice</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>reduce quantity of chocolate and add nuts of your choice</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>chicken marinated with tsp gochujang paste</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>200 grams chicken marinated with 1/2 tsp gochujang paste</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>rice flour mixed with cup water</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>1 tbsp rice flour mixed with 1/4 cup water</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>boombayway vegan garlic mayo</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" t="inlineStr">
         <is>
           <t>3 tbsp @boombayway vegan garlic mayo</t>
         </is>
